--- a/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
+++ b/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M279"/>
+  <dimension ref="A1:O279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,16 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>anio</t>
         </is>
       </c>
@@ -538,7 +548,17 @@
           <t>150123</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -597,7 +617,17 @@
           <t>150122</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -656,7 +686,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -715,7 +755,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -774,7 +824,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -833,7 +893,17 @@
           <t>150140</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -892,7 +962,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -951,7 +1031,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1010,7 +1100,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1069,7 +1169,17 @@
           <t>150119</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1128,7 +1238,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1187,7 +1307,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1246,7 +1376,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1305,7 +1445,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1364,7 +1514,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1423,7 +1583,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1482,7 +1652,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1541,7 +1721,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1600,7 +1790,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1659,7 +1859,17 @@
           <t>150123</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1718,7 +1928,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1777,7 +1997,17 @@
           <t>150120</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1836,7 +2066,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1895,7 +2135,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -1954,7 +2204,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2013,7 +2273,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2072,7 +2342,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2131,7 +2411,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2190,7 +2480,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2249,7 +2549,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2308,7 +2618,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2367,7 +2687,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2426,7 +2756,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2485,7 +2825,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2544,7 +2894,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2603,7 +2963,17 @@
           <t>150120</t>
         </is>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2662,7 +3032,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2721,7 +3101,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2780,7 +3170,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2839,7 +3239,17 @@
           <t>150122</t>
         </is>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2898,7 +3308,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -2957,7 +3377,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3016,7 +3446,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3075,7 +3515,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3134,7 +3584,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M46" t="n">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3193,7 +3653,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3252,7 +3722,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3311,7 +3791,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3370,7 +3860,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M50" t="n">
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3429,7 +3929,17 @@
           <t>150139</t>
         </is>
       </c>
-      <c r="M51" t="n">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3488,7 +3998,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3547,7 +4067,17 @@
           <t>150134</t>
         </is>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3606,7 +4136,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M54" t="n">
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3665,7 +4205,17 @@
           <t>150124</t>
         </is>
       </c>
-      <c r="M55" t="n">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3724,7 +4274,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M56" t="n">
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3783,7 +4343,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M57" t="n">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3842,7 +4412,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M58" t="n">
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3901,7 +4481,17 @@
           <t>150121</t>
         </is>
       </c>
-      <c r="M59" t="n">
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -3960,7 +4550,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M60" t="n">
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4019,7 +4619,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M61" t="n">
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4078,7 +4688,17 @@
           <t>150102</t>
         </is>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4137,7 +4757,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M63" t="n">
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4196,7 +4826,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M64" t="n">
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4255,7 +4895,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4314,7 +4964,17 @@
           <t>150112</t>
         </is>
       </c>
-      <c r="M66" t="n">
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4373,7 +5033,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M67" t="n">
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4432,7 +5102,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M68" t="n">
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4491,7 +5171,17 @@
           <t>150123</t>
         </is>
       </c>
-      <c r="M69" t="n">
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4550,7 +5240,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M70" t="n">
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4609,7 +5309,17 @@
           <t>150131</t>
         </is>
       </c>
-      <c r="M71" t="n">
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4668,7 +5378,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M72" t="n">
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4727,7 +5447,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M73" t="n">
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4786,7 +5516,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M74" t="n">
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4845,7 +5585,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M75" t="n">
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4904,7 +5654,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M76" t="n">
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -4963,7 +5723,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M77" t="n">
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5022,7 +5792,17 @@
           <t>150109</t>
         </is>
       </c>
-      <c r="M78" t="n">
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5081,7 +5861,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M79" t="n">
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5140,7 +5930,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M80" t="n">
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5199,7 +5999,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M81" t="n">
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5258,7 +6068,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M82" t="n">
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5317,7 +6137,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M83" t="n">
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5376,7 +6206,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M84" t="n">
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5435,7 +6275,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M85" t="n">
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5494,7 +6344,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M86" t="n">
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5529,7 +6389,9 @@
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="n">
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5588,7 +6450,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M88" t="n">
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5647,7 +6519,17 @@
           <t>150137</t>
         </is>
       </c>
-      <c r="M89" t="n">
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5706,7 +6588,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M90" t="n">
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5765,7 +6657,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M91" t="n">
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5824,7 +6726,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M92" t="n">
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5883,7 +6795,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M93" t="n">
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -5942,7 +6864,17 @@
           <t>150134</t>
         </is>
       </c>
-      <c r="M94" t="n">
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6001,7 +6933,17 @@
           <t>150134</t>
         </is>
       </c>
-      <c r="M95" t="n">
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6060,7 +7002,17 @@
           <t>150102</t>
         </is>
       </c>
-      <c r="M96" t="n">
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6119,7 +7071,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M97" t="n">
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6178,7 +7140,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M98" t="n">
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6237,7 +7209,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M99" t="n">
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6296,7 +7278,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M100" t="n">
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6355,7 +7347,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M101" t="n">
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6414,7 +7416,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M102" t="n">
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6473,7 +7485,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M103" t="n">
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6532,7 +7554,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M104" t="n">
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6591,7 +7623,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M105" t="n">
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6650,7 +7692,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M106" t="n">
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6709,7 +7761,17 @@
           <t>150106</t>
         </is>
       </c>
-      <c r="M107" t="n">
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6768,7 +7830,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M108" t="n">
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6827,7 +7899,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M109" t="n">
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6886,7 +7968,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M110" t="n">
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -6945,7 +8037,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M111" t="n">
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7004,7 +8106,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M112" t="n">
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7063,7 +8175,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M113" t="n">
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7122,7 +8244,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M114" t="n">
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7181,7 +8313,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M115" t="n">
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7240,7 +8382,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M116" t="n">
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7299,7 +8451,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M117" t="n">
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7358,7 +8520,17 @@
           <t>150102</t>
         </is>
       </c>
-      <c r="M118" t="n">
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7417,7 +8589,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M119" t="n">
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7476,7 +8658,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M120" t="n">
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7535,7 +8727,17 @@
           <t>150141</t>
         </is>
       </c>
-      <c r="M121" t="n">
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7594,7 +8796,17 @@
           <t>150131</t>
         </is>
       </c>
-      <c r="M122" t="n">
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7653,7 +8865,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M123" t="n">
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7712,7 +8934,17 @@
           <t>150123</t>
         </is>
       </c>
-      <c r="M124" t="n">
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7771,7 +9003,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M125" t="n">
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O125" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7830,7 +9072,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M126" t="n">
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O126" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7889,7 +9141,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M127" t="n">
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O127" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -7948,7 +9210,17 @@
           <t>150106</t>
         </is>
       </c>
-      <c r="M128" t="n">
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8007,7 +9279,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M129" t="n">
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8066,7 +9348,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M130" t="n">
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O130" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8125,7 +9417,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M131" t="n">
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O131" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8184,7 +9486,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M132" t="n">
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8243,7 +9555,17 @@
           <t>150118</t>
         </is>
       </c>
-      <c r="M133" t="n">
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O133" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8302,7 +9624,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M134" t="n">
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O134" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8361,7 +9693,17 @@
           <t>150120</t>
         </is>
       </c>
-      <c r="M135" t="n">
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O135" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8420,7 +9762,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M136" t="n">
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O136" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8479,7 +9831,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M137" t="n">
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O137" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8538,7 +9900,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M138" t="n">
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O138" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8597,7 +9969,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M139" t="n">
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O139" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8656,7 +10038,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M140" t="n">
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O140" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8715,7 +10107,17 @@
           <t>150140</t>
         </is>
       </c>
-      <c r="M141" t="n">
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O141" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8774,7 +10176,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M142" t="n">
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8833,7 +10245,17 @@
           <t>150130</t>
         </is>
       </c>
-      <c r="M143" t="n">
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O143" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8892,7 +10314,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M144" t="n">
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -8951,7 +10383,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M145" t="n">
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9010,7 +10452,17 @@
           <t>150112</t>
         </is>
       </c>
-      <c r="M146" t="n">
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9069,7 +10521,17 @@
           <t>150113</t>
         </is>
       </c>
-      <c r="M147" t="n">
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O147" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9128,7 +10590,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M148" t="n">
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9187,7 +10659,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M149" t="n">
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O149" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9246,7 +10728,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M150" t="n">
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O150" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9305,7 +10797,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M151" t="n">
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O151" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9364,7 +10866,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M152" t="n">
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O152" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9423,7 +10935,17 @@
           <t>150106</t>
         </is>
       </c>
-      <c r="M153" t="n">
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O153" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9482,7 +11004,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M154" t="n">
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O154" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9541,7 +11073,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M155" t="n">
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9600,7 +11142,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M156" t="n">
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9659,7 +11211,17 @@
           <t>150120</t>
         </is>
       </c>
-      <c r="M157" t="n">
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9718,7 +11280,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M158" t="n">
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9777,7 +11349,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M159" t="n">
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9836,7 +11418,17 @@
           <t>150112</t>
         </is>
       </c>
-      <c r="M160" t="n">
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9895,7 +11487,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M161" t="n">
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -9954,7 +11556,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M162" t="n">
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10013,7 +11625,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M163" t="n">
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10072,7 +11694,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M164" t="n">
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10131,7 +11763,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M165" t="n">
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10190,7 +11832,17 @@
           <t>150106</t>
         </is>
       </c>
-      <c r="M166" t="n">
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10249,7 +11901,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M167" t="n">
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10308,7 +11970,17 @@
           <t>150123</t>
         </is>
       </c>
-      <c r="M168" t="n">
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10367,7 +12039,17 @@
           <t>150119</t>
         </is>
       </c>
-      <c r="M169" t="n">
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10426,7 +12108,17 @@
           <t>150123</t>
         </is>
       </c>
-      <c r="M170" t="n">
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10485,7 +12177,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M171" t="n">
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10544,7 +12246,17 @@
           <t>150136</t>
         </is>
       </c>
-      <c r="M172" t="n">
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10603,7 +12315,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M173" t="n">
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10662,7 +12384,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M174" t="n">
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10721,7 +12453,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M175" t="n">
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10780,7 +12522,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M176" t="n">
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10839,7 +12591,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M177" t="n">
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10898,7 +12660,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M178" t="n">
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -10957,7 +12729,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M179" t="n">
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11016,7 +12798,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M180" t="n">
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11075,7 +12867,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M181" t="n">
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11134,7 +12936,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M182" t="n">
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11193,7 +13005,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M183" t="n">
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11252,7 +13074,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M184" t="n">
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11311,7 +13143,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M185" t="n">
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11370,7 +13212,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M186" t="n">
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11429,7 +13281,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M187" t="n">
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11488,7 +13350,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M188" t="n">
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O188" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11547,7 +13419,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M189" t="n">
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O189" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11606,7 +13488,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M190" t="n">
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O190" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11665,7 +13557,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M191" t="n">
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O191" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11724,7 +13626,17 @@
           <t>150107</t>
         </is>
       </c>
-      <c r="M192" t="n">
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11783,7 +13695,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M193" t="n">
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O193" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11842,7 +13764,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M194" t="n">
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O194" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11901,7 +13833,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M195" t="n">
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O195" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -11960,7 +13902,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M196" t="n">
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O196" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12019,7 +13971,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M197" t="n">
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O197" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12078,7 +14040,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M198" t="n">
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O198" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12137,7 +14109,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M199" t="n">
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O199" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12196,7 +14178,17 @@
           <t>150142</t>
         </is>
       </c>
-      <c r="M200" t="n">
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O200" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12255,7 +14247,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M201" t="n">
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O201" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12314,7 +14316,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M202" t="n">
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O202" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12373,7 +14385,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M203" t="n">
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O203" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12432,7 +14454,17 @@
           <t>150140</t>
         </is>
       </c>
-      <c r="M204" t="n">
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O204" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12491,7 +14523,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M205" t="n">
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O205" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12550,7 +14592,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M206" t="n">
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O206" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12609,7 +14661,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M207" t="n">
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O207" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12668,7 +14730,17 @@
           <t>150121</t>
         </is>
       </c>
-      <c r="M208" t="n">
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O208" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12727,7 +14799,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M209" t="n">
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O209" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12786,7 +14868,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M210" t="n">
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O210" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12845,7 +14937,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M211" t="n">
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O211" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12904,7 +15006,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M212" t="n">
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O212" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -12963,7 +15075,17 @@
           <t>150121</t>
         </is>
       </c>
-      <c r="M213" t="n">
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O213" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13022,7 +15144,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M214" t="n">
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O214" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13081,7 +15213,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M215" t="n">
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O215" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13140,7 +15282,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M216" t="n">
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O216" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13199,7 +15351,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M217" t="n">
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O217" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13258,7 +15420,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M218" t="n">
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O218" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13315,7 +15487,17 @@
           <t>150120</t>
         </is>
       </c>
-      <c r="M219" t="n">
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O219" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13372,7 +15554,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M220" t="n">
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O220" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13429,7 +15621,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M221" t="n">
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O221" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13486,7 +15688,17 @@
           <t>150124</t>
         </is>
       </c>
-      <c r="M222" t="n">
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O222" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13543,7 +15755,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M223" t="n">
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O223" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13600,7 +15822,17 @@
           <t>150133</t>
         </is>
       </c>
-      <c r="M224" t="n">
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O224" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13657,7 +15889,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M225" t="n">
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O225" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13714,7 +15956,17 @@
           <t>150108</t>
         </is>
       </c>
-      <c r="M226" t="n">
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O226" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13771,7 +16023,17 @@
           <t>150121</t>
         </is>
       </c>
-      <c r="M227" t="n">
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O227" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13828,7 +16090,17 @@
           <t>150119</t>
         </is>
       </c>
-      <c r="M228" t="n">
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O228" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13885,7 +16157,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M229" t="n">
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O229" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13942,7 +16224,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M230" t="n">
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O230" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -13999,7 +16291,17 @@
           <t>150125</t>
         </is>
       </c>
-      <c r="M231" t="n">
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O231" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14056,7 +16358,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M232" t="n">
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O232" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14113,7 +16425,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M233" t="n">
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O233" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14170,7 +16492,17 @@
           <t>150106</t>
         </is>
       </c>
-      <c r="M234" t="n">
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O234" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14227,7 +16559,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M235" t="n">
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O235" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14284,7 +16626,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M236" t="n">
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O236" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14341,7 +16693,17 @@
           <t>150118</t>
         </is>
       </c>
-      <c r="M237" t="n">
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O237" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14398,7 +16760,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M238" t="n">
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O238" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14455,7 +16827,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M239" t="n">
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O239" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14512,7 +16894,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M240" t="n">
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O240" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14569,7 +16961,17 @@
           <t>150121</t>
         </is>
       </c>
-      <c r="M241" t="n">
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O241" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14626,7 +17028,17 @@
           <t>150143</t>
         </is>
       </c>
-      <c r="M242" t="n">
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O242" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14683,7 +17095,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M243" t="n">
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O243" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14740,7 +17162,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M244" t="n">
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O244" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14797,7 +17229,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M245" t="n">
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O245" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14854,7 +17296,17 @@
           <t>150113</t>
         </is>
       </c>
-      <c r="M246" t="n">
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O246" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14911,7 +17363,17 @@
           <t>150120</t>
         </is>
       </c>
-      <c r="M247" t="n">
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O247" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -14968,7 +17430,17 @@
           <t>150141</t>
         </is>
       </c>
-      <c r="M248" t="n">
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O248" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15025,7 +17497,17 @@
           <t>150141</t>
         </is>
       </c>
-      <c r="M249" t="n">
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O249" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15082,7 +17564,17 @@
           <t>150130</t>
         </is>
       </c>
-      <c r="M250" t="n">
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
+      <c r="O250" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15139,7 +17631,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M251" t="n">
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O251" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15196,7 +17698,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M252" t="n">
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O252" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15253,7 +17765,17 @@
           <t>150107</t>
         </is>
       </c>
-      <c r="M253" t="n">
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O253" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15310,7 +17832,17 @@
           <t>150123</t>
         </is>
       </c>
-      <c r="M254" t="n">
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O254" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15367,7 +17899,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M255" t="n">
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O255" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15424,7 +17966,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M256" t="n">
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O256" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15481,7 +18033,17 @@
           <t>150142</t>
         </is>
       </c>
-      <c r="M257" t="n">
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O257" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15538,7 +18100,17 @@
           <t>150101</t>
         </is>
       </c>
-      <c r="M258" t="n">
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O258" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15595,7 +18167,17 @@
           <t>150121</t>
         </is>
       </c>
-      <c r="M259" t="n">
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O259" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15652,7 +18234,17 @@
           <t>150112</t>
         </is>
       </c>
-      <c r="M260" t="n">
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O260" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15709,7 +18301,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M261" t="n">
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O261" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15766,7 +18368,17 @@
           <t>150124</t>
         </is>
       </c>
-      <c r="M262" t="n">
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
+      <c r="O262" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15823,7 +18435,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M263" t="n">
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O263" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15880,7 +18502,17 @@
           <t>150105</t>
         </is>
       </c>
-      <c r="M264" t="n">
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O264" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15937,7 +18569,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M265" t="n">
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O265" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -15994,7 +18636,17 @@
           <t>150135</t>
         </is>
       </c>
-      <c r="M266" t="n">
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O266" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16031,7 +18683,9 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
-      <c r="M267" t="n">
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16088,7 +18742,17 @@
           <t>150121</t>
         </is>
       </c>
-      <c r="M268" t="n">
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O268" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16145,7 +18809,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M269" t="n">
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O269" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16202,7 +18876,17 @@
           <t>150132</t>
         </is>
       </c>
-      <c r="M270" t="n">
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O270" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16259,7 +18943,17 @@
           <t>150103</t>
         </is>
       </c>
-      <c r="M271" t="n">
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O271" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16316,7 +19010,17 @@
           <t>150128</t>
         </is>
       </c>
-      <c r="M272" t="n">
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O272" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16373,7 +19077,17 @@
           <t>150115</t>
         </is>
       </c>
-      <c r="M273" t="n">
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O273" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16430,7 +19144,17 @@
           <t>150107</t>
         </is>
       </c>
-      <c r="M274" t="n">
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
+      <c r="O274" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16487,7 +19211,17 @@
           <t>150120</t>
         </is>
       </c>
-      <c r="M275" t="n">
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
+      <c r="O275" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16544,7 +19278,17 @@
           <t>150117</t>
         </is>
       </c>
-      <c r="M276" t="n">
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
+      <c r="O276" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16601,7 +19345,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M277" t="n">
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O277" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16658,7 +19412,17 @@
           <t>150110</t>
         </is>
       </c>
-      <c r="M278" t="n">
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
+      <c r="O278" t="n">
         <v>2026</v>
       </c>
     </row>
@@ -16715,7 +19479,17 @@
           <t>150111</t>
         </is>
       </c>
-      <c r="M279" t="n">
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
+      <c r="O279" t="n">
         <v>2026</v>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
+++ b/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O279"/>
+  <dimension ref="A1:P279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,11 @@
           <t>anio</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -561,6 +566,11 @@
       <c r="O2" t="n">
         <v>2026</v>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -630,6 +640,11 @@
       <c r="O3" t="n">
         <v>2026</v>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -699,6 +714,11 @@
       <c r="O4" t="n">
         <v>2026</v>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -768,6 +788,11 @@
       <c r="O5" t="n">
         <v>2026</v>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -837,6 +862,11 @@
       <c r="O6" t="n">
         <v>2026</v>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -906,6 +936,11 @@
       <c r="O7" t="n">
         <v>2026</v>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -975,6 +1010,11 @@
       <c r="O8" t="n">
         <v>2026</v>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1044,6 +1084,11 @@
       <c r="O9" t="n">
         <v>2026</v>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1113,6 +1158,11 @@
       <c r="O10" t="n">
         <v>2026</v>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1182,6 +1232,11 @@
       <c r="O11" t="n">
         <v>2026</v>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1251,6 +1306,11 @@
       <c r="O12" t="n">
         <v>2026</v>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1320,6 +1380,11 @@
       <c r="O13" t="n">
         <v>2026</v>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1389,6 +1454,11 @@
       <c r="O14" t="n">
         <v>2026</v>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1458,6 +1528,11 @@
       <c r="O15" t="n">
         <v>2026</v>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1527,6 +1602,11 @@
       <c r="O16" t="n">
         <v>2026</v>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1596,6 +1676,11 @@
       <c r="O17" t="n">
         <v>2026</v>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1665,6 +1750,11 @@
       <c r="O18" t="n">
         <v>2026</v>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1734,6 +1824,11 @@
       <c r="O19" t="n">
         <v>2026</v>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1803,6 +1898,11 @@
       <c r="O20" t="n">
         <v>2026</v>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1872,6 +1972,11 @@
       <c r="O21" t="n">
         <v>2026</v>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1941,6 +2046,11 @@
       <c r="O22" t="n">
         <v>2026</v>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2010,6 +2120,11 @@
       <c r="O23" t="n">
         <v>2026</v>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2079,6 +2194,11 @@
       <c r="O24" t="n">
         <v>2026</v>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2148,6 +2268,11 @@
       <c r="O25" t="n">
         <v>2026</v>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2217,6 +2342,11 @@
       <c r="O26" t="n">
         <v>2026</v>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2286,6 +2416,11 @@
       <c r="O27" t="n">
         <v>2026</v>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2355,6 +2490,11 @@
       <c r="O28" t="n">
         <v>2026</v>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2424,6 +2564,11 @@
       <c r="O29" t="n">
         <v>2026</v>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2493,6 +2638,11 @@
       <c r="O30" t="n">
         <v>2026</v>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2562,6 +2712,11 @@
       <c r="O31" t="n">
         <v>2026</v>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2631,6 +2786,11 @@
       <c r="O32" t="n">
         <v>2026</v>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2700,6 +2860,11 @@
       <c r="O33" t="n">
         <v>2026</v>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2769,6 +2934,11 @@
       <c r="O34" t="n">
         <v>2026</v>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2838,6 +3008,11 @@
       <c r="O35" t="n">
         <v>2026</v>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2907,6 +3082,11 @@
       <c r="O36" t="n">
         <v>2026</v>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2976,6 +3156,11 @@
       <c r="O37" t="n">
         <v>2026</v>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3045,6 +3230,11 @@
       <c r="O38" t="n">
         <v>2026</v>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3114,6 +3304,11 @@
       <c r="O39" t="n">
         <v>2026</v>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3183,6 +3378,11 @@
       <c r="O40" t="n">
         <v>2026</v>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3252,6 +3452,11 @@
       <c r="O41" t="n">
         <v>2026</v>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3321,6 +3526,11 @@
       <c r="O42" t="n">
         <v>2026</v>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3390,6 +3600,11 @@
       <c r="O43" t="n">
         <v>2026</v>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3459,6 +3674,11 @@
       <c r="O44" t="n">
         <v>2026</v>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3528,6 +3748,11 @@
       <c r="O45" t="n">
         <v>2026</v>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3597,6 +3822,11 @@
       <c r="O46" t="n">
         <v>2026</v>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3666,6 +3896,11 @@
       <c r="O47" t="n">
         <v>2026</v>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3735,6 +3970,11 @@
       <c r="O48" t="n">
         <v>2026</v>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3804,6 +4044,11 @@
       <c r="O49" t="n">
         <v>2026</v>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3873,6 +4118,11 @@
       <c r="O50" t="n">
         <v>2026</v>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3942,6 +4192,11 @@
       <c r="O51" t="n">
         <v>2026</v>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4011,6 +4266,11 @@
       <c r="O52" t="n">
         <v>2026</v>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4080,6 +4340,11 @@
       <c r="O53" t="n">
         <v>2026</v>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4149,6 +4414,11 @@
       <c r="O54" t="n">
         <v>2026</v>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4218,6 +4488,11 @@
       <c r="O55" t="n">
         <v>2026</v>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4287,6 +4562,11 @@
       <c r="O56" t="n">
         <v>2026</v>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4356,6 +4636,11 @@
       <c r="O57" t="n">
         <v>2026</v>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4425,6 +4710,11 @@
       <c r="O58" t="n">
         <v>2026</v>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4494,6 +4784,11 @@
       <c r="O59" t="n">
         <v>2026</v>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4563,6 +4858,11 @@
       <c r="O60" t="n">
         <v>2026</v>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4632,6 +4932,11 @@
       <c r="O61" t="n">
         <v>2026</v>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4701,6 +5006,11 @@
       <c r="O62" t="n">
         <v>2026</v>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4770,6 +5080,11 @@
       <c r="O63" t="n">
         <v>2026</v>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4839,6 +5154,11 @@
       <c r="O64" t="n">
         <v>2026</v>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4908,6 +5228,11 @@
       <c r="O65" t="n">
         <v>2026</v>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4977,6 +5302,11 @@
       <c r="O66" t="n">
         <v>2026</v>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5046,6 +5376,11 @@
       <c r="O67" t="n">
         <v>2026</v>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5115,6 +5450,11 @@
       <c r="O68" t="n">
         <v>2026</v>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5184,6 +5524,11 @@
       <c r="O69" t="n">
         <v>2026</v>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5253,6 +5598,11 @@
       <c r="O70" t="n">
         <v>2026</v>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5322,6 +5672,11 @@
       <c r="O71" t="n">
         <v>2026</v>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5391,6 +5746,11 @@
       <c r="O72" t="n">
         <v>2026</v>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5460,6 +5820,11 @@
       <c r="O73" t="n">
         <v>2026</v>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5529,6 +5894,11 @@
       <c r="O74" t="n">
         <v>2026</v>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5598,6 +5968,11 @@
       <c r="O75" t="n">
         <v>2026</v>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5667,6 +6042,11 @@
       <c r="O76" t="n">
         <v>2026</v>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5736,6 +6116,11 @@
       <c r="O77" t="n">
         <v>2026</v>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5805,6 +6190,11 @@
       <c r="O78" t="n">
         <v>2026</v>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5874,6 +6264,11 @@
       <c r="O79" t="n">
         <v>2026</v>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5943,6 +6338,11 @@
       <c r="O80" t="n">
         <v>2026</v>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6012,6 +6412,11 @@
       <c r="O81" t="n">
         <v>2026</v>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6081,6 +6486,11 @@
       <c r="O82" t="n">
         <v>2026</v>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6150,6 +6560,11 @@
       <c r="O83" t="n">
         <v>2026</v>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6219,6 +6634,11 @@
       <c r="O84" t="n">
         <v>2026</v>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6288,6 +6708,11 @@
       <c r="O85" t="n">
         <v>2026</v>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6357,6 +6782,11 @@
       <c r="O86" t="n">
         <v>2026</v>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6384,15 +6814,44 @@
       <c r="G87" t="n">
         <v>301588</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>150142</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
       <c r="O87" t="n">
         <v>2026</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -6463,6 +6922,11 @@
       <c r="O88" t="n">
         <v>2026</v>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6532,6 +6996,11 @@
       <c r="O89" t="n">
         <v>2026</v>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6601,6 +7070,11 @@
       <c r="O90" t="n">
         <v>2026</v>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6670,6 +7144,11 @@
       <c r="O91" t="n">
         <v>2026</v>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6739,6 +7218,11 @@
       <c r="O92" t="n">
         <v>2026</v>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6808,6 +7292,11 @@
       <c r="O93" t="n">
         <v>2026</v>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6877,6 +7366,11 @@
       <c r="O94" t="n">
         <v>2026</v>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6946,6 +7440,11 @@
       <c r="O95" t="n">
         <v>2026</v>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7015,6 +7514,11 @@
       <c r="O96" t="n">
         <v>2026</v>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7084,6 +7588,11 @@
       <c r="O97" t="n">
         <v>2026</v>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7153,6 +7662,11 @@
       <c r="O98" t="n">
         <v>2026</v>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7222,6 +7736,11 @@
       <c r="O99" t="n">
         <v>2026</v>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7291,6 +7810,11 @@
       <c r="O100" t="n">
         <v>2026</v>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7360,6 +7884,11 @@
       <c r="O101" t="n">
         <v>2026</v>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7429,6 +7958,11 @@
       <c r="O102" t="n">
         <v>2026</v>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7498,6 +8032,11 @@
       <c r="O103" t="n">
         <v>2026</v>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7567,6 +8106,11 @@
       <c r="O104" t="n">
         <v>2026</v>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7636,6 +8180,11 @@
       <c r="O105" t="n">
         <v>2026</v>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7705,6 +8254,11 @@
       <c r="O106" t="n">
         <v>2026</v>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7774,6 +8328,11 @@
       <c r="O107" t="n">
         <v>2026</v>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7843,6 +8402,11 @@
       <c r="O108" t="n">
         <v>2026</v>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7912,6 +8476,11 @@
       <c r="O109" t="n">
         <v>2026</v>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7981,6 +8550,11 @@
       <c r="O110" t="n">
         <v>2026</v>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8050,6 +8624,11 @@
       <c r="O111" t="n">
         <v>2026</v>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8119,6 +8698,11 @@
       <c r="O112" t="n">
         <v>2026</v>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8188,6 +8772,11 @@
       <c r="O113" t="n">
         <v>2026</v>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8257,6 +8846,11 @@
       <c r="O114" t="n">
         <v>2026</v>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8326,6 +8920,11 @@
       <c r="O115" t="n">
         <v>2026</v>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8395,6 +8994,11 @@
       <c r="O116" t="n">
         <v>2026</v>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8464,6 +9068,11 @@
       <c r="O117" t="n">
         <v>2026</v>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8533,6 +9142,11 @@
       <c r="O118" t="n">
         <v>2026</v>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8602,6 +9216,11 @@
       <c r="O119" t="n">
         <v>2026</v>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8671,6 +9290,11 @@
       <c r="O120" t="n">
         <v>2026</v>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8740,6 +9364,11 @@
       <c r="O121" t="n">
         <v>2026</v>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8809,6 +9438,11 @@
       <c r="O122" t="n">
         <v>2026</v>
       </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8878,6 +9512,11 @@
       <c r="O123" t="n">
         <v>2026</v>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8947,6 +9586,11 @@
       <c r="O124" t="n">
         <v>2026</v>
       </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9016,6 +9660,11 @@
       <c r="O125" t="n">
         <v>2026</v>
       </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9085,6 +9734,11 @@
       <c r="O126" t="n">
         <v>2026</v>
       </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9154,6 +9808,11 @@
       <c r="O127" t="n">
         <v>2026</v>
       </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9223,6 +9882,11 @@
       <c r="O128" t="n">
         <v>2026</v>
       </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9292,6 +9956,11 @@
       <c r="O129" t="n">
         <v>2026</v>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9361,6 +10030,11 @@
       <c r="O130" t="n">
         <v>2026</v>
       </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9430,6 +10104,11 @@
       <c r="O131" t="n">
         <v>2026</v>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9499,6 +10178,11 @@
       <c r="O132" t="n">
         <v>2026</v>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9568,6 +10252,11 @@
       <c r="O133" t="n">
         <v>2026</v>
       </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9637,6 +10326,11 @@
       <c r="O134" t="n">
         <v>2026</v>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9706,6 +10400,11 @@
       <c r="O135" t="n">
         <v>2026</v>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9775,6 +10474,11 @@
       <c r="O136" t="n">
         <v>2026</v>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9844,6 +10548,11 @@
       <c r="O137" t="n">
         <v>2026</v>
       </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9913,6 +10622,11 @@
       <c r="O138" t="n">
         <v>2026</v>
       </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9982,6 +10696,11 @@
       <c r="O139" t="n">
         <v>2026</v>
       </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10051,6 +10770,11 @@
       <c r="O140" t="n">
         <v>2026</v>
       </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -10120,6 +10844,11 @@
       <c r="O141" t="n">
         <v>2026</v>
       </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10189,6 +10918,11 @@
       <c r="O142" t="n">
         <v>2026</v>
       </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10258,6 +10992,11 @@
       <c r="O143" t="n">
         <v>2026</v>
       </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10327,6 +11066,11 @@
       <c r="O144" t="n">
         <v>2026</v>
       </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10396,6 +11140,11 @@
       <c r="O145" t="n">
         <v>2026</v>
       </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10465,6 +11214,11 @@
       <c r="O146" t="n">
         <v>2026</v>
       </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10534,6 +11288,11 @@
       <c r="O147" t="n">
         <v>2026</v>
       </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10603,6 +11362,11 @@
       <c r="O148" t="n">
         <v>2026</v>
       </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10672,6 +11436,11 @@
       <c r="O149" t="n">
         <v>2026</v>
       </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10741,6 +11510,11 @@
       <c r="O150" t="n">
         <v>2026</v>
       </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10810,6 +11584,11 @@
       <c r="O151" t="n">
         <v>2026</v>
       </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10879,6 +11658,11 @@
       <c r="O152" t="n">
         <v>2026</v>
       </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10948,6 +11732,11 @@
       <c r="O153" t="n">
         <v>2026</v>
       </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -11017,6 +11806,11 @@
       <c r="O154" t="n">
         <v>2026</v>
       </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -11086,6 +11880,11 @@
       <c r="O155" t="n">
         <v>2026</v>
       </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -11155,6 +11954,11 @@
       <c r="O156" t="n">
         <v>2026</v>
       </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -11224,6 +12028,11 @@
       <c r="O157" t="n">
         <v>2026</v>
       </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11293,6 +12102,11 @@
       <c r="O158" t="n">
         <v>2026</v>
       </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11362,6 +12176,11 @@
       <c r="O159" t="n">
         <v>2026</v>
       </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11431,6 +12250,11 @@
       <c r="O160" t="n">
         <v>2026</v>
       </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11500,6 +12324,11 @@
       <c r="O161" t="n">
         <v>2026</v>
       </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11569,6 +12398,11 @@
       <c r="O162" t="n">
         <v>2026</v>
       </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11638,6 +12472,11 @@
       <c r="O163" t="n">
         <v>2026</v>
       </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11707,6 +12546,11 @@
       <c r="O164" t="n">
         <v>2026</v>
       </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11776,6 +12620,11 @@
       <c r="O165" t="n">
         <v>2026</v>
       </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11845,6 +12694,11 @@
       <c r="O166" t="n">
         <v>2026</v>
       </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11914,6 +12768,11 @@
       <c r="O167" t="n">
         <v>2026</v>
       </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11983,6 +12842,11 @@
       <c r="O168" t="n">
         <v>2026</v>
       </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -12052,6 +12916,11 @@
       <c r="O169" t="n">
         <v>2026</v>
       </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12121,6 +12990,11 @@
       <c r="O170" t="n">
         <v>2026</v>
       </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12190,6 +13064,11 @@
       <c r="O171" t="n">
         <v>2026</v>
       </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12259,6 +13138,11 @@
       <c r="O172" t="n">
         <v>2026</v>
       </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12328,6 +13212,11 @@
       <c r="O173" t="n">
         <v>2026</v>
       </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12397,6 +13286,11 @@
       <c r="O174" t="n">
         <v>2026</v>
       </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12466,6 +13360,11 @@
       <c r="O175" t="n">
         <v>2026</v>
       </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12535,6 +13434,11 @@
       <c r="O176" t="n">
         <v>2026</v>
       </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12604,6 +13508,11 @@
       <c r="O177" t="n">
         <v>2026</v>
       </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12673,6 +13582,11 @@
       <c r="O178" t="n">
         <v>2026</v>
       </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12742,6 +13656,11 @@
       <c r="O179" t="n">
         <v>2026</v>
       </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12811,6 +13730,11 @@
       <c r="O180" t="n">
         <v>2026</v>
       </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12880,6 +13804,11 @@
       <c r="O181" t="n">
         <v>2026</v>
       </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12949,6 +13878,11 @@
       <c r="O182" t="n">
         <v>2026</v>
       </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -13018,6 +13952,11 @@
       <c r="O183" t="n">
         <v>2026</v>
       </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13087,6 +14026,11 @@
       <c r="O184" t="n">
         <v>2026</v>
       </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13156,6 +14100,11 @@
       <c r="O185" t="n">
         <v>2026</v>
       </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13225,6 +14174,11 @@
       <c r="O186" t="n">
         <v>2026</v>
       </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13294,6 +14248,11 @@
       <c r="O187" t="n">
         <v>2026</v>
       </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13363,6 +14322,11 @@
       <c r="O188" t="n">
         <v>2026</v>
       </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13432,6 +14396,11 @@
       <c r="O189" t="n">
         <v>2026</v>
       </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13501,6 +14470,11 @@
       <c r="O190" t="n">
         <v>2026</v>
       </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13570,6 +14544,11 @@
       <c r="O191" t="n">
         <v>2026</v>
       </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13639,6 +14618,11 @@
       <c r="O192" t="n">
         <v>2026</v>
       </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13708,6 +14692,11 @@
       <c r="O193" t="n">
         <v>2026</v>
       </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13777,6 +14766,11 @@
       <c r="O194" t="n">
         <v>2026</v>
       </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13846,6 +14840,11 @@
       <c r="O195" t="n">
         <v>2026</v>
       </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13915,6 +14914,11 @@
       <c r="O196" t="n">
         <v>2026</v>
       </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13984,6 +14988,11 @@
       <c r="O197" t="n">
         <v>2026</v>
       </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14053,6 +15062,11 @@
       <c r="O198" t="n">
         <v>2026</v>
       </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14122,6 +15136,11 @@
       <c r="O199" t="n">
         <v>2026</v>
       </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14191,6 +15210,11 @@
       <c r="O200" t="n">
         <v>2026</v>
       </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14260,6 +15284,11 @@
       <c r="O201" t="n">
         <v>2026</v>
       </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14329,6 +15358,11 @@
       <c r="O202" t="n">
         <v>2026</v>
       </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14398,6 +15432,11 @@
       <c r="O203" t="n">
         <v>2026</v>
       </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14467,6 +15506,11 @@
       <c r="O204" t="n">
         <v>2026</v>
       </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14536,6 +15580,11 @@
       <c r="O205" t="n">
         <v>2026</v>
       </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14605,6 +15654,11 @@
       <c r="O206" t="n">
         <v>2026</v>
       </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14674,6 +15728,11 @@
       <c r="O207" t="n">
         <v>2026</v>
       </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14743,6 +15802,11 @@
       <c r="O208" t="n">
         <v>2026</v>
       </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14812,6 +15876,11 @@
       <c r="O209" t="n">
         <v>2026</v>
       </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14881,6 +15950,11 @@
       <c r="O210" t="n">
         <v>2026</v>
       </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14950,6 +16024,11 @@
       <c r="O211" t="n">
         <v>2026</v>
       </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15019,6 +16098,11 @@
       <c r="O212" t="n">
         <v>2026</v>
       </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -15088,6 +16172,11 @@
       <c r="O213" t="n">
         <v>2026</v>
       </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15157,6 +16246,11 @@
       <c r="O214" t="n">
         <v>2026</v>
       </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15226,6 +16320,11 @@
       <c r="O215" t="n">
         <v>2026</v>
       </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15295,6 +16394,11 @@
       <c r="O216" t="n">
         <v>2026</v>
       </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15364,6 +16468,11 @@
       <c r="O217" t="n">
         <v>2026</v>
       </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15433,6 +16542,11 @@
       <c r="O218" t="n">
         <v>2026</v>
       </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -15500,6 +16614,11 @@
       <c r="O219" t="n">
         <v>2026</v>
       </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15567,6 +16686,11 @@
       <c r="O220" t="n">
         <v>2026</v>
       </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -15634,6 +16758,11 @@
       <c r="O221" t="n">
         <v>2026</v>
       </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -15701,6 +16830,11 @@
       <c r="O222" t="n">
         <v>2026</v>
       </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -15768,6 +16902,11 @@
       <c r="O223" t="n">
         <v>2026</v>
       </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -15835,6 +16974,11 @@
       <c r="O224" t="n">
         <v>2026</v>
       </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -15902,6 +17046,11 @@
       <c r="O225" t="n">
         <v>2026</v>
       </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -15969,6 +17118,11 @@
       <c r="O226" t="n">
         <v>2026</v>
       </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -16036,6 +17190,11 @@
       <c r="O227" t="n">
         <v>2026</v>
       </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16103,6 +17262,11 @@
       <c r="O228" t="n">
         <v>2026</v>
       </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -16170,6 +17334,11 @@
       <c r="O229" t="n">
         <v>2026</v>
       </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -16237,6 +17406,11 @@
       <c r="O230" t="n">
         <v>2026</v>
       </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -16304,6 +17478,11 @@
       <c r="O231" t="n">
         <v>2026</v>
       </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -16371,6 +17550,11 @@
       <c r="O232" t="n">
         <v>2026</v>
       </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -16438,6 +17622,11 @@
       <c r="O233" t="n">
         <v>2026</v>
       </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16505,6 +17694,11 @@
       <c r="O234" t="n">
         <v>2026</v>
       </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -16572,6 +17766,11 @@
       <c r="O235" t="n">
         <v>2026</v>
       </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -16639,6 +17838,11 @@
       <c r="O236" t="n">
         <v>2026</v>
       </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -16706,6 +17910,11 @@
       <c r="O237" t="n">
         <v>2026</v>
       </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -16773,6 +17982,11 @@
       <c r="O238" t="n">
         <v>2026</v>
       </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -16840,6 +18054,11 @@
       <c r="O239" t="n">
         <v>2026</v>
       </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -16907,6 +18126,11 @@
       <c r="O240" t="n">
         <v>2026</v>
       </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -16974,6 +18198,11 @@
       <c r="O241" t="n">
         <v>2026</v>
       </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -17041,6 +18270,11 @@
       <c r="O242" t="n">
         <v>2026</v>
       </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -17108,6 +18342,11 @@
       <c r="O243" t="n">
         <v>2026</v>
       </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -17175,6 +18414,11 @@
       <c r="O244" t="n">
         <v>2026</v>
       </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -17242,6 +18486,11 @@
       <c r="O245" t="n">
         <v>2026</v>
       </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -17309,6 +18558,11 @@
       <c r="O246" t="n">
         <v>2026</v>
       </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17376,6 +18630,11 @@
       <c r="O247" t="n">
         <v>2026</v>
       </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17443,6 +18702,11 @@
       <c r="O248" t="n">
         <v>2026</v>
       </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -17510,6 +18774,11 @@
       <c r="O249" t="n">
         <v>2026</v>
       </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17577,6 +18846,11 @@
       <c r="O250" t="n">
         <v>2026</v>
       </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -17644,6 +18918,11 @@
       <c r="O251" t="n">
         <v>2026</v>
       </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -17711,6 +18990,11 @@
       <c r="O252" t="n">
         <v>2026</v>
       </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -17778,6 +19062,11 @@
       <c r="O253" t="n">
         <v>2026</v>
       </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -17845,6 +19134,11 @@
       <c r="O254" t="n">
         <v>2026</v>
       </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17912,6 +19206,11 @@
       <c r="O255" t="n">
         <v>2026</v>
       </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -17979,6 +19278,11 @@
       <c r="O256" t="n">
         <v>2026</v>
       </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -18046,6 +19350,11 @@
       <c r="O257" t="n">
         <v>2026</v>
       </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18113,6 +19422,11 @@
       <c r="O258" t="n">
         <v>2026</v>
       </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -18180,6 +19494,11 @@
       <c r="O259" t="n">
         <v>2026</v>
       </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18247,6 +19566,11 @@
       <c r="O260" t="n">
         <v>2026</v>
       </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -18314,6 +19638,11 @@
       <c r="O261" t="n">
         <v>2026</v>
       </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -18381,6 +19710,11 @@
       <c r="O262" t="n">
         <v>2026</v>
       </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -18448,6 +19782,11 @@
       <c r="O263" t="n">
         <v>2026</v>
       </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18515,6 +19854,11 @@
       <c r="O264" t="n">
         <v>2026</v>
       </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -18582,6 +19926,11 @@
       <c r="O265" t="n">
         <v>2026</v>
       </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -18648,6 +19997,11 @@
       </c>
       <c r="O266" t="n">
         <v>2026</v>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -18688,6 +20042,11 @@
       <c r="O267" t="n">
         <v>2026</v>
       </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -18755,6 +20114,11 @@
       <c r="O268" t="n">
         <v>2026</v>
       </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -18822,6 +20186,11 @@
       <c r="O269" t="n">
         <v>2026</v>
       </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -18889,6 +20258,11 @@
       <c r="O270" t="n">
         <v>2026</v>
       </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -18956,6 +20330,11 @@
       <c r="O271" t="n">
         <v>2026</v>
       </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19023,6 +20402,11 @@
       <c r="O272" t="n">
         <v>2026</v>
       </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -19090,6 +20474,11 @@
       <c r="O273" t="n">
         <v>2026</v>
       </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -19157,6 +20546,11 @@
       <c r="O274" t="n">
         <v>2026</v>
       </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -19224,6 +20618,11 @@
       <c r="O275" t="n">
         <v>2026</v>
       </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -19291,6 +20690,11 @@
       <c r="O276" t="n">
         <v>2026</v>
       </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -19358,6 +20762,11 @@
       <c r="O277" t="n">
         <v>2026</v>
       </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -19425,6 +20834,11 @@
       <c r="O278" t="n">
         <v>2026</v>
       </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -19491,6 +20905,11 @@
       </c>
       <c r="O279" t="n">
         <v>2026</v>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>DRELM</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
+++ b/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P279"/>
+  <dimension ref="A1:R279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,10 +489,20 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>anio</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -563,10 +573,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v>2026</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6016 JESUS SALVADOR/6016 JESUS SALVADOR</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -637,10 +657,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>2026</v>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>7003 MANUEL FERNANDO BONILLA</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -711,10 +741,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>2026</v>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0115 23 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -785,10 +825,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O5" t="n">
-        <v>2026</v>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0115 01 LA SEMILLITA</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -859,10 +909,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O6" t="n">
-        <v>2026</v>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>7062 NACIONES UNIDAS/7062 NACIONES UNIDAS</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -933,10 +993,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>2026</v>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>7058 MARIA DE FATIMA</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1007,10 +1077,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O8" t="n">
-        <v>2026</v>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7064 MARIA AUXILIADORA/7064 MARIA AUXILIADORA/7064 MARIA AUXILIADORA</t>
+        </is>
       </c>
       <c r="P8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1081,10 +1161,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O9" t="n">
-        <v>2026</v>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1016 JOHN F. KENNEDY</t>
+        </is>
       </c>
       <c r="P9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1155,10 +1245,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O10" t="n">
-        <v>2026</v>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6032 ALMIRANTE MIGUEL GRAU SEMINARIO/6032 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+        </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1229,10 +1329,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O11" t="n">
-        <v>2026</v>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6008 JOSE ANTONIO DAPELO/6008 JOSE ANTONIO DAPELO</t>
+        </is>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1303,10 +1413,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O12" t="n">
-        <v>2026</v>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>629-6034 CESAR CARBONEL RODRIGUEZ/629-6034 CESAR CARBONEL RODRIGUEZ</t>
+        </is>
       </c>
       <c r="P12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1377,10 +1497,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O13" t="n">
-        <v>2026</v>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6015 SANTISIMO SAGRADO CORAZON DE JESUS</t>
+        </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1451,10 +1581,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O14" t="n">
-        <v>2026</v>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>21 SAN BENITO DE PALERMO</t>
+        </is>
       </c>
       <c r="P14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1525,10 +1665,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O15" t="n">
-        <v>2026</v>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>105 PEDRO CORONADO ARRASCUE/105 PEDRO CORONADO ARRASCUE</t>
+        </is>
       </c>
       <c r="P15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1599,10 +1749,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O16" t="n">
-        <v>2026</v>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
       </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1673,10 +1833,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O17" t="n">
-        <v>2026</v>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>1006 MARISCAL ANDRES AVELINO CACERES/1006 MARISCAL ANDRES AVELINO CACERES</t>
+        </is>
       </c>
       <c r="P17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1747,10 +1917,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O18" t="n">
-        <v>2026</v>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>7077 LOS REYES ROJOS/7077 LOS REYES ROJOS/7077 LOS REYES ROJOS</t>
+        </is>
       </c>
       <c r="P18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1821,10 +2001,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>2026</v>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1047 JUANA INFANTES VERA/1047 JUANA INFANTES VERA/1047 JUANA INFANTES VERA</t>
+        </is>
       </c>
       <c r="P19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1895,10 +2085,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O20" t="n">
-        <v>2026</v>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1244 MICAELA BASTIDAS/1244 MICAELA BASTIDAS/1244 MICAELA BASTIDAS</t>
+        </is>
       </c>
       <c r="P20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -1969,10 +2169,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O21" t="n">
-        <v>2026</v>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>7259 VICTOR R. HAYA DE LA TORRE/7259 VICTOR R. HAYA DE LA TORRE/656 MI PEQUEÑO MUNDO</t>
+        </is>
       </c>
       <c r="P21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2043,10 +2253,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O22" t="n">
-        <v>2026</v>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0156 EL PORVENIR/0156 EL PORVENIR</t>
+        </is>
       </c>
       <c r="P22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2117,10 +2337,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O23" t="n">
-        <v>2026</v>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI</t>
+        </is>
       </c>
       <c r="P23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2191,10 +2421,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O24" t="n">
-        <v>2026</v>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>3019 PATRICIA TERESA RODRIGUEZ/3019 PATRICIA TERESA RODRIGUEZ</t>
+        </is>
       </c>
       <c r="P24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2265,10 +2505,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O25" t="n">
-        <v>2026</v>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>3014 LEONCIO PRADO</t>
+        </is>
       </c>
       <c r="P25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2339,10 +2589,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O26" t="n">
-        <v>2026</v>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>3033 ANDRES AVELINO CACERES/3033 ANDRES AVELINO CACERES</t>
+        </is>
       </c>
       <c r="P26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2413,10 +2673,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O27" t="n">
-        <v>2026</v>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>TUPAC AMARU II</t>
+        </is>
       </c>
       <c r="P27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2487,10 +2757,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O28" t="n">
-        <v>2026</v>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2003 LIBERTADOR JOSE DE SAN MARTIN/2003 LIBERTADOR JOSE DE SAN MARTIN/2003 LIBERTADOR JOSE DE SAN MARTIN/2003 LIBERTADOR JOSE DE SAN MARTIN</t>
+        </is>
       </c>
       <c r="P28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2561,10 +2841,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O29" t="n">
-        <v>2026</v>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0091 SANTA FE/0091 SANTA FE</t>
+        </is>
       </c>
       <c r="P29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2635,10 +2925,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O30" t="n">
-        <v>2026</v>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0099 OSCAR MIRO QUESADA DE LA GUERRA/0099 OSCAR MIRO QUESADA DE LA GUERRA</t>
+        </is>
       </c>
       <c r="P30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R30" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2709,10 +3009,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O31" t="n">
-        <v>2026</v>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>6081 MANUEL SCORZA TORRES/6081 MANUEL SCORZA TORRES/6081 MANUEL SCORZA TORRES/6081 MANUEL SCORZA TORRES</t>
+        </is>
       </c>
       <c r="P31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2783,10 +3093,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O32" t="n">
-        <v>2026</v>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>7081 JOSE MARIA ARGUEDAS A/7081 JOSE MARIA ARGUEDAS A</t>
+        </is>
       </c>
       <c r="P32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R32" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2857,10 +3177,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O33" t="n">
-        <v>2026</v>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>6059 SAGRADO CORAZON DE JESUS/6059 SAGRADO CORAZON DE JESUS/6059 SAGRADO CORAZON DE JESUS</t>
+        </is>
       </c>
       <c r="P33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -2931,10 +3261,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O34" t="n">
-        <v>2026</v>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>6019 MARIANO MELGAR/6019 MARIANO MELGAR</t>
+        </is>
       </c>
       <c r="P34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3005,10 +3345,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O35" t="n">
-        <v>2026</v>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>LOS INKAS/LOS INKAS/LOS INKAS</t>
+        </is>
       </c>
       <c r="P35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R35" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3079,10 +3429,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O36" t="n">
-        <v>2026</v>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>123 PAUL HARRIS</t>
+        </is>
       </c>
       <c r="P36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R36" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3153,10 +3513,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O37" t="n">
-        <v>2026</v>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>126 VIRGEN DEL CARMEN</t>
+        </is>
       </c>
       <c r="P37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3227,10 +3597,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O38" t="n">
-        <v>2026</v>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>7044 SAN MARTIN DE PORRES</t>
+        </is>
       </c>
       <c r="P38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3301,10 +3681,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O39" t="n">
-        <v>2026</v>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>7052 MARIA INMACULADA</t>
+        </is>
       </c>
       <c r="P39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R39" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3375,10 +3765,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O40" t="n">
-        <v>2026</v>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>151 MICAELA BASTIDAS/151 MICAELA BASTIDAS/151 MICAELA BASTIDAS/151 MICAELA BASTIDAS</t>
+        </is>
       </c>
       <c r="P40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R40" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3449,10 +3849,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O41" t="n">
-        <v>2026</v>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7001 ANDRES BELLO</t>
+        </is>
       </c>
       <c r="P41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3523,10 +3933,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O42" t="n">
-        <v>2026</v>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3597,10 +4017,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O43" t="n">
-        <v>2026</v>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1171 JORGE BASADRE GROHMANN/1171 JORGE BASADRE GROHMANN/1171 JORGE BASADRE GROHMANN</t>
+        </is>
       </c>
       <c r="P43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3671,10 +4101,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O44" t="n">
-        <v>2026</v>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS</t>
+        </is>
       </c>
       <c r="P44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R44" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3745,10 +4185,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O45" t="n">
-        <v>2026</v>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1048 VIRGEN PURISIMA</t>
+        </is>
       </c>
       <c r="P45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R45" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3819,10 +4269,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O46" t="n">
-        <v>2026</v>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1145 REPUBLICA DE VENEZUELA/1145 REPUBLICA DE VENEZUELA</t>
+        </is>
       </c>
       <c r="P46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3893,10 +4353,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O47" t="n">
-        <v>2026</v>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>210 MARIA PARADO DE BELLIDO</t>
+        </is>
       </c>
       <c r="P47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R47" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -3967,10 +4437,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O48" t="n">
-        <v>2026</v>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA</t>
+        </is>
       </c>
       <c r="P48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R48" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4041,10 +4521,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O49" t="n">
-        <v>2026</v>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>604 LAS BEGONIAS</t>
+        </is>
       </c>
       <c r="P49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4115,10 +4605,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O50" t="n">
-        <v>2026</v>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
       </c>
       <c r="P50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4189,10 +4689,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O51" t="n">
-        <v>2026</v>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
       </c>
       <c r="P51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R51" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4263,10 +4773,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O52" t="n">
-        <v>2026</v>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>112 HEROES DE LA BREÑA/112 HEROES DE LA BREÑA</t>
+        </is>
       </c>
       <c r="P52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4337,10 +4857,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O53" t="n">
-        <v>2026</v>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1216 MIGUEL GRAU SEMINARIO/1216 MIGUEL GRAU SEMINARIO</t>
+        </is>
       </c>
       <c r="P53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R53" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4411,10 +4941,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O54" t="n">
-        <v>2026</v>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>LA ALBORADA FRANCESA</t>
+        </is>
       </c>
       <c r="P54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4485,10 +5025,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O55" t="n">
-        <v>2026</v>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>7257 MENOTTI BIFFI GARIBOTTO/7257 MENOTTI BIFFI GARIBOTTO</t>
+        </is>
       </c>
       <c r="P55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R55" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4559,10 +5109,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O56" t="n">
-        <v>2026</v>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4633,10 +5193,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O57" t="n">
-        <v>2026</v>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>3081 ALMIRANTE MIGUEL GRAU SEMINARIO/3081 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+        </is>
       </c>
       <c r="P57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R57" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4707,10 +5277,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O58" t="n">
-        <v>2026</v>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NUEVO PERU/NUEVO PERU</t>
+        </is>
       </c>
       <c r="P58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4781,10 +5361,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O59" t="n">
-        <v>2026</v>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>1073 HERMANN BUSE DE LA GUERRA/1073 HERMANN BUSE DE LA GUERRA</t>
+        </is>
       </c>
       <c r="P59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R59" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4855,10 +5445,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O60" t="n">
-        <v>2026</v>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>112 HEROES DE LA BREÑA/112 HEROES DE LA BREÑA</t>
+        </is>
       </c>
       <c r="P60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -4929,10 +5529,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O61" t="n">
-        <v>2026</v>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NIÑO JOEL I Y JOEL II</t>
+        </is>
       </c>
       <c r="P61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R61" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5003,10 +5613,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O62" t="n">
-        <v>2026</v>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>CARLOS GUTIERREZ MERINO</t>
+        </is>
       </c>
       <c r="P62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R62" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5077,10 +5697,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O63" t="n">
-        <v>2026</v>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
       </c>
       <c r="P63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5151,10 +5781,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O64" t="n">
-        <v>2026</v>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>563 SANTISIMO DIVINO NIÑO JESUS</t>
+        </is>
       </c>
       <c r="P64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R64" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5225,10 +5865,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O65" t="n">
-        <v>2026</v>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>100 VIRGEN DE LA MERCED</t>
+        </is>
       </c>
       <c r="P65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R65" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5299,10 +5949,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O66" t="n">
-        <v>2026</v>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0392</t>
+        </is>
       </c>
       <c r="P66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R66" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5373,10 +6033,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O67" t="n">
-        <v>2026</v>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>185 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5447,10 +6117,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O68" t="n">
-        <v>2026</v>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
       </c>
       <c r="P68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5521,10 +6201,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O69" t="n">
-        <v>2026</v>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>6006 SANTISIMA VIRGEN DE LOURDES</t>
+        </is>
       </c>
       <c r="P69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R69" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5595,10 +6285,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O70" t="n">
-        <v>2026</v>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>PEREGRINOS DEL SEÑOR</t>
+        </is>
       </c>
       <c r="P70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R70" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5669,10 +6369,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O71" t="n">
-        <v>2026</v>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1051 EL OLIVAR/1051 EL OLIVAR</t>
+        </is>
       </c>
       <c r="P71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R71" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5743,10 +6453,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O72" t="n">
-        <v>2026</v>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1244 MICAELA BASTIDAS/1244 MICAELA BASTIDAS/1244 MICAELA BASTIDAS</t>
+        </is>
       </c>
       <c r="P72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R72" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5817,10 +6537,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O73" t="n">
-        <v>2026</v>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>116 SAN PABLO</t>
+        </is>
       </c>
       <c r="P73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R73" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5891,10 +6621,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O74" t="n">
-        <v>2026</v>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>8162</t>
+        </is>
       </c>
       <c r="P74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R74" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -5965,10 +6705,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O75" t="n">
-        <v>2026</v>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2007 ROSA DE LAS AMERICAS/2007 ROSA DE LAS AMERICAS</t>
+        </is>
       </c>
       <c r="P75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R75" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6039,10 +6789,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O76" t="n">
-        <v>2026</v>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>8156 PERUANO ALEMAN</t>
+        </is>
       </c>
       <c r="P76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R76" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6113,10 +6873,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O77" t="n">
-        <v>2026</v>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>1252 SANTA ISABEL/1252 SANTA ISABEL</t>
+        </is>
       </c>
       <c r="P77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R77" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6187,10 +6957,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O78" t="n">
-        <v>2026</v>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>1261 GUILLERMO WAGNER</t>
+        </is>
       </c>
       <c r="P78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R78" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6261,10 +7041,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O79" t="n">
-        <v>2026</v>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>5170 PERU ITALIA</t>
+        </is>
       </c>
       <c r="P79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6335,10 +7125,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O80" t="n">
-        <v>2026</v>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>6059 SAGRADO CORAZON DE JESUS/6059 SAGRADO CORAZON DE JESUS/6059 SAGRADO CORAZON DE JESUS</t>
+        </is>
       </c>
       <c r="P80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6409,10 +7209,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O81" t="n">
-        <v>2026</v>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
       </c>
       <c r="P81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R81" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6483,10 +7293,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O82" t="n">
-        <v>2026</v>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2008 EL ROSARIO/2008 EL ROSARIO</t>
+        </is>
       </c>
       <c r="P82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6557,10 +7377,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O83" t="n">
-        <v>2026</v>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>010 MARTIR OLAYA</t>
+        </is>
       </c>
       <c r="P83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R83" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6631,10 +7461,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O84" t="n">
-        <v>2026</v>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION/25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION/25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION</t>
+        </is>
       </c>
       <c r="P84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R84" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6705,10 +7545,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O85" t="n">
-        <v>2026</v>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>3055 TUPAC AMARU/3055 TUPAC AMARU/3055 TUPAC AMARU/3055 TUPAC AMARU</t>
+        </is>
       </c>
       <c r="P85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6779,10 +7629,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O86" t="n">
-        <v>2026</v>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>PRIMERO DE MAYO 2</t>
+        </is>
       </c>
       <c r="P86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R86" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6845,10 +7705,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O87" t="n">
-        <v>2026</v>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>MI PEQUEÑO HOGAR</t>
+        </is>
       </c>
       <c r="P87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R87" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6919,10 +7789,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O88" t="n">
-        <v>2026</v>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>SEMILLITAS</t>
+        </is>
       </c>
       <c r="P88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R88" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -6993,10 +7873,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O89" t="n">
-        <v>2026</v>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>MIS PRIMEROS PASOS</t>
+        </is>
       </c>
       <c r="P89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R89" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7067,10 +7957,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O90" t="n">
-        <v>2026</v>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>27 DE MARZO/27 DE MARZO</t>
+        </is>
       </c>
       <c r="P90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R90" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7141,10 +8041,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O91" t="n">
-        <v>2026</v>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>7041 VIRGEN DE LA MERCED/7041 VIRGEN DE LA MERCED</t>
+        </is>
       </c>
       <c r="P91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R91" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7215,10 +8125,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O92" t="n">
-        <v>2026</v>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1008 VIRGEN DE LOURDES/1008 VIRGEN DE LOURDES</t>
+        </is>
       </c>
       <c r="P92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R92" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7289,10 +8209,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O93" t="n">
-        <v>2026</v>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>161 MOISES COLONIA TRINIDAD/161 MOISES COLONIA TRINIDAD/161 MOISES COLONIA TRINIDAD</t>
+        </is>
       </c>
       <c r="P93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R93" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7363,10 +8293,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O94" t="n">
-        <v>2026</v>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>133 FERNANDO LUNA DEMUTTI</t>
+        </is>
       </c>
       <c r="P94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R94" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7437,10 +8377,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O95" t="n">
-        <v>2026</v>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="P95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R95" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7511,10 +8461,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O96" t="n">
-        <v>2026</v>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>615 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R96" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7585,10 +8545,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O97" t="n">
-        <v>2026</v>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0049 ANTONIA MORENO DE CACERES/0049 ANTONIA MORENO DE CACERES</t>
+        </is>
       </c>
       <c r="P97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R97" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7659,10 +8629,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O98" t="n">
-        <v>2026</v>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>7064 MARIA AUXILIADORA/7064 MARIA AUXILIADORA/7064 MARIA AUXILIADORA</t>
+        </is>
       </c>
       <c r="P98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R98" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7733,10 +8713,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O99" t="n">
-        <v>2026</v>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1145 REPUBLICA DE VENEZUELA/1145 REPUBLICA DE VENEZUELA</t>
+        </is>
       </c>
       <c r="P99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R99" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7807,10 +8797,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O100" t="n">
-        <v>2026</v>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1040 REPUBLICA DE HAITI/1040 REPUBLICA DE HAITI</t>
+        </is>
       </c>
       <c r="P100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R100" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7881,10 +8881,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O101" t="n">
-        <v>2026</v>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0004 MARIANO MELGAR/0004 MARIANO MELGAR</t>
+        </is>
       </c>
       <c r="P101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R101" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -7955,10 +8965,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O102" t="n">
-        <v>2026</v>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>VISION MUNDIAL/VISION MUNDIAL/VISION MUNDIAL</t>
+        </is>
       </c>
       <c r="P102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R102" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8029,10 +9049,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O103" t="n">
-        <v>2026</v>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>115-15 NIÑO JESUS</t>
+        </is>
       </c>
       <c r="P103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R103" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8103,10 +9133,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O104" t="n">
-        <v>2026</v>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
       </c>
       <c r="P104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R104" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8177,10 +9217,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O105" t="n">
-        <v>2026</v>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>7077 LOS REYES ROJOS/7077 LOS REYES ROJOS/7077 LOS REYES ROJOS</t>
+        </is>
       </c>
       <c r="P105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R105" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8251,10 +9301,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O106" t="n">
-        <v>2026</v>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>1015 REPUBLICA DE ITALIA/1015 REPUBLICA DE ITALIA</t>
+        </is>
       </c>
       <c r="P106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R106" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8325,10 +9385,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O107" t="n">
-        <v>2026</v>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
       </c>
       <c r="P107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R107" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8399,10 +9469,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O108" t="n">
-        <v>2026</v>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS</t>
+        </is>
       </c>
       <c r="P108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R108" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8473,10 +9553,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O109" t="n">
-        <v>2026</v>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>195 ANGELITOS DE JESUS</t>
+        </is>
       </c>
       <c r="P109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R109" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8547,10 +9637,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O110" t="n">
-        <v>2026</v>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>1015 REPUBLICA DE ITALIA/1015 REPUBLICA DE ITALIA</t>
+        </is>
       </c>
       <c r="P110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R110" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8621,10 +9721,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O111" t="n">
-        <v>2026</v>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>1174 VIRGEN DEL CARMEN/1174 VIRGEN DEL CARMEN/1174 VIRGEN DEL CARMEN</t>
+        </is>
       </c>
       <c r="P111" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R111" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8695,10 +9805,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O112" t="n">
-        <v>2026</v>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2095 HERMAN BUSSE DE LA GUERRA/2095 HERMAN BUSSE DE LA GUERRA/2095 HERMAN BUSSE DE LA GUERRA/2095 HERMAN BUSSE DE LA GUERRA</t>
+        </is>
       </c>
       <c r="P112" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R112" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8769,10 +9889,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O113" t="n">
-        <v>2026</v>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2008 EL ROSARIO/2008 EL ROSARIO</t>
+        </is>
       </c>
       <c r="P113" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R113" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8843,10 +9973,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O114" t="n">
-        <v>2026</v>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2085 SAN AGUSTIN/2085 SAN AGUSTIN</t>
+        </is>
       </c>
       <c r="P114" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R114" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8917,10 +10057,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O115" t="n">
-        <v>2026</v>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>1187 SAN CAYETANO/1187 SAN CAYETANO</t>
+        </is>
       </c>
       <c r="P115" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R115" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -8991,10 +10141,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O116" t="n">
-        <v>2026</v>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>0076 MARIA AUXILIADORA/0076 MARIA AUXILIADORA</t>
+        </is>
       </c>
       <c r="P116" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R116" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9065,10 +10225,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O117" t="n">
-        <v>2026</v>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>1008 VIRGEN DE LOURDES/1008 VIRGEN DE LOURDES</t>
+        </is>
       </c>
       <c r="P117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R117" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9139,10 +10309,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O118" t="n">
-        <v>2026</v>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>594 JESUS AMIGO</t>
+        </is>
       </c>
       <c r="P118" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R118" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9213,10 +10393,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O119" t="n">
-        <v>2026</v>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2007 ROSA DE LAS AMERICAS/2007 ROSA DE LAS AMERICAS</t>
+        </is>
       </c>
       <c r="P119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R119" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9287,10 +10477,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O120" t="n">
-        <v>2026</v>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>3068 SAN JUDAS TADEO/3068 SAN JUDAS TADEO</t>
+        </is>
       </c>
       <c r="P120" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R120" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9361,10 +10561,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O121" t="n">
-        <v>2026</v>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>LA DIVINA PROVIDENCIA</t>
+        </is>
       </c>
       <c r="P121" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R121" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9435,10 +10645,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O122" t="n">
-        <v>2026</v>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>1051 EL OLIVAR/1051 EL OLIVAR</t>
+        </is>
       </c>
       <c r="P122" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R122" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9509,10 +10729,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O123" t="n">
-        <v>2026</v>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>110 SAN MARCOS/110 SAN MARCOS</t>
+        </is>
       </c>
       <c r="P123" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R123" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9583,10 +10813,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O124" t="n">
-        <v>2026</v>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>7258/7258</t>
+        </is>
       </c>
       <c r="P124" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R124" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9657,10 +10897,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O125" t="n">
-        <v>2026</v>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>0140 SANTIAGO ANTUNEZ DE MAYOLO/0140 SANTIAGO ANTUNEZ DE MAYOLO</t>
+        </is>
       </c>
       <c r="P125" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R125" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9731,10 +10981,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O126" t="n">
-        <v>2026</v>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>1152-108 DOS DE MAYO/1152-108 DOS DE MAYO</t>
+        </is>
       </c>
       <c r="P126" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R126" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9805,10 +11065,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O127" t="n">
-        <v>2026</v>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>1162 DIVINO NIÑO JESUS</t>
+        </is>
       </c>
       <c r="P127" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R127" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9879,10 +11149,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O128" t="n">
-        <v>2026</v>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>359 MANDILITO AZUL</t>
+        </is>
       </c>
       <c r="P128" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R128" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -9953,10 +11233,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O129" t="n">
-        <v>2026</v>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>0069 MACHU PICCHU/0069 MACHU PICCHU</t>
+        </is>
       </c>
       <c r="P129" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R129" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10027,10 +11317,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O130" t="n">
-        <v>2026</v>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>2025 INMACULADA CONCEPCION/2025 INMACULADA CONCEPCION</t>
+        </is>
       </c>
       <c r="P130" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R130" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10101,10 +11401,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O131" t="n">
-        <v>2026</v>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA</t>
+        </is>
       </c>
       <c r="P131" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R131" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10175,10 +11485,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O132" t="n">
-        <v>2026</v>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>DULCE AMANECER</t>
+        </is>
       </c>
       <c r="P132" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R132" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10249,10 +11569,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O133" t="n">
-        <v>2026</v>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>0058 CUSCO/0058 CUSCO</t>
+        </is>
       </c>
       <c r="P133" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R133" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10323,10 +11653,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O134" t="n">
-        <v>2026</v>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>1105 LA SAGRADA FAMILIA/1105 LA SAGRADA FAMILIA/1105 LA SAGRADA FAMILIA</t>
+        </is>
       </c>
       <c r="P134" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R134" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10397,10 +11737,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O135" t="n">
-        <v>2026</v>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>1104 CRNEL. FAP VICTOR MALDONADO BEGAZO</t>
+        </is>
       </c>
       <c r="P135" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R135" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10471,10 +11821,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O136" t="n">
-        <v>2026</v>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>94 MICAELA BASTIDAS</t>
+        </is>
       </c>
       <c r="P136" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R136" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10545,10 +11905,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O137" t="n">
-        <v>2026</v>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>0389 VIRGEN DE LOURDES</t>
+        </is>
       </c>
       <c r="P137" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R137" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10619,10 +11989,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O138" t="n">
-        <v>2026</v>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>134 RAMIRO PRIALE/134 RAMIRO PRIALE/134 RAMIRO PRIALE</t>
+        </is>
       </c>
       <c r="P138" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R138" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10693,10 +12073,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O139" t="n">
-        <v>2026</v>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>01 SAN JUDAS TADEO</t>
+        </is>
       </c>
       <c r="P139" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R139" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10767,10 +12157,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O140" t="n">
-        <v>2026</v>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>LOS ANGELITOS DEL DIVINO NIÑO</t>
+        </is>
       </c>
       <c r="P140" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R140" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10841,10 +12241,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O141" t="n">
-        <v>2026</v>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>VICTORIA BARCIA BONIFFATTI</t>
+        </is>
       </c>
       <c r="P141" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R141" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10915,10 +12325,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O142" t="n">
-        <v>2026</v>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>1119 NUESTRA SEÑORA DEL ROSARIO DE FATIMA/1119 NUESTRA SEÑORA DEL ROSARIO DE FATIMA</t>
+        </is>
       </c>
       <c r="P142" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R142" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -10989,10 +12409,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O143" t="n">
-        <v>2026</v>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>528 ALEGRIA DE JESUS</t>
+        </is>
       </c>
       <c r="P143" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R143" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11063,10 +12493,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O144" t="n">
-        <v>2026</v>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS/111 SAN JOSE DE ARTESANOS</t>
+        </is>
       </c>
       <c r="P144" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R144" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11137,10 +12577,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O145" t="n">
-        <v>2026</v>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>7208/7208</t>
+        </is>
       </c>
       <c r="P145" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R145" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11211,10 +12661,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O146" t="n">
-        <v>2026</v>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>0390-1 EL ERMITAÑO</t>
+        </is>
       </c>
       <c r="P146" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R146" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11285,10 +12745,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O147" t="n">
-        <v>2026</v>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>GABRIELA MISTRAL</t>
+        </is>
       </c>
       <c r="P147" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R147" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11359,10 +12829,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O148" t="n">
-        <v>2026</v>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>VISION MUNDIAL/VISION MUNDIAL/VISION MUNDIAL</t>
+        </is>
       </c>
       <c r="P148" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R148" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11433,10 +12913,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O149" t="n">
-        <v>2026</v>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>161 MOISES COLONIA TRINIDAD/161 MOISES COLONIA TRINIDAD/161 MOISES COLONIA TRINIDAD</t>
+        </is>
       </c>
       <c r="P149" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R149" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11507,10 +12997,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O150" t="n">
-        <v>2026</v>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>125 RICARDO PALMA/125 RICARDO PALMA</t>
+        </is>
       </c>
       <c r="P150" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R150" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11581,10 +13081,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O151" t="n">
-        <v>2026</v>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>0073 BENITO JUAREZ/0073 BENITO JUAREZ</t>
+        </is>
       </c>
       <c r="P151" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R151" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11655,10 +13165,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O152" t="n">
-        <v>2026</v>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>3073 EL DORADO/3073 EL DORADO</t>
+        </is>
       </c>
       <c r="P152" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R152" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11729,10 +13249,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O153" t="n">
-        <v>2026</v>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>8161 MANUEL SCORZA TORRE/8161 MANUEL SCORZA TORRE</t>
+        </is>
       </c>
       <c r="P153" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R153" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11803,10 +13333,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O154" t="n">
-        <v>2026</v>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>0038 VIRGEN MEDALLA MILAGROSA</t>
+        </is>
       </c>
       <c r="P154" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R154" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11877,10 +13417,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O155" t="n">
-        <v>2026</v>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>018 OKINAWA</t>
+        </is>
       </c>
       <c r="P155" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R155" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -11951,10 +13501,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O156" t="n">
-        <v>2026</v>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>3033 ANDRES AVELINO CACERES/3033 ANDRES AVELINO CACERES</t>
+        </is>
       </c>
       <c r="P156" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R156" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12025,10 +13585,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O157" t="n">
-        <v>2026</v>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI</t>
+        </is>
       </c>
       <c r="P157" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R157" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12099,10 +13669,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O158" t="n">
-        <v>2026</v>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>8176 NUEVA ESPERANZA</t>
+        </is>
       </c>
       <c r="P158" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R158" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12173,10 +13753,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O159" t="n">
-        <v>2026</v>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>3017 INMACULADA CONCEPCION/3017 INMACULADA CONCEPCION</t>
+        </is>
       </c>
       <c r="P159" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R159" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12247,10 +13837,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O160" t="n">
-        <v>2026</v>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>2052 MARIA AUXILIADORA/2052 MARIA AUXILIADORA/2052 MARIA AUXILIADORA</t>
+        </is>
       </c>
       <c r="P160" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R160" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12321,10 +13921,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O161" t="n">
-        <v>2026</v>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>3073 EL DORADO/3073 EL DORADO</t>
+        </is>
       </c>
       <c r="P161" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R161" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12395,10 +14005,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O162" t="n">
-        <v>2026</v>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>3085 PEDRO VILCA APAZA</t>
+        </is>
       </c>
       <c r="P162" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R162" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12469,10 +14089,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O163" t="n">
-        <v>2026</v>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>MODULO LAS ANIMAS</t>
+        </is>
       </c>
       <c r="P163" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R163" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12543,10 +14173,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O164" t="n">
-        <v>2026</v>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
       </c>
       <c r="P164" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R164" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12617,10 +14257,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O165" t="n">
-        <v>2026</v>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>125 RICARDO PALMA/125 RICARDO PALMA</t>
+        </is>
       </c>
       <c r="P165" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R165" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12691,10 +14341,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O166" t="n">
-        <v>2026</v>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>8161 MANUEL SCORZA TORRE/8161 MANUEL SCORZA TORRE</t>
+        </is>
       </c>
       <c r="P166" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R166" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12765,10 +14425,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O167" t="n">
-        <v>2026</v>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>LIBERTAD/LIBERTAD/LIBERTAD</t>
+        </is>
       </c>
       <c r="P167" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R167" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12839,10 +14509,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O168" t="n">
-        <v>2026</v>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>7263 ROXANITA CASTRO WITTING</t>
+        </is>
       </c>
       <c r="P168" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R168" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12913,10 +14593,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O169" t="n">
-        <v>2026</v>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>6008 JOSE ANTONIO DAPELO/6008 JOSE ANTONIO DAPELO</t>
+        </is>
       </c>
       <c r="P169" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R169" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -12987,10 +14677,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O170" t="n">
-        <v>2026</v>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>6016 JESUS SALVADOR/6016 JESUS SALVADOR</t>
+        </is>
       </c>
       <c r="P170" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R170" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13061,10 +14761,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O171" t="n">
-        <v>2026</v>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION/25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION/25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION</t>
+        </is>
       </c>
       <c r="P171" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R171" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13135,10 +14845,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O172" t="n">
-        <v>2026</v>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>24 ROSA IRENE INFANTES DE CANALES</t>
+        </is>
       </c>
       <c r="P172" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R172" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13209,10 +14929,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O173" t="n">
-        <v>2026</v>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>3001 ESTADOS UNIDOS MEXICANOS</t>
+        </is>
       </c>
       <c r="P173" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R173" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13283,10 +15013,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O174" t="n">
-        <v>2026</v>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>3019 PATRICIA TERESA RODRIGUEZ/3019 PATRICIA TERESA RODRIGUEZ</t>
+        </is>
       </c>
       <c r="P174" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R174" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13357,10 +15097,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O175" t="n">
-        <v>2026</v>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>7081 JOSE MARIA ARGUEDAS A/7081 JOSE MARIA ARGUEDAS A</t>
+        </is>
       </c>
       <c r="P175" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R175" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13431,10 +15181,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O176" t="n">
-        <v>2026</v>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>151 MICAELA BASTIDAS/151 MICAELA BASTIDAS/151 MICAELA BASTIDAS/151 MICAELA BASTIDAS</t>
+        </is>
       </c>
       <c r="P176" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R176" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13505,10 +15265,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O177" t="n">
-        <v>2026</v>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>SAN CARLOS</t>
+        </is>
       </c>
       <c r="P177" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R177" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13579,10 +15349,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O178" t="n">
-        <v>2026</v>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>2091 MARISCAL ANDRES AVELINO CACERES/2091 MARISCAL ANDRES AVELINO CACERES</t>
+        </is>
       </c>
       <c r="P178" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R178" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13653,10 +15433,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O179" t="n">
-        <v>2026</v>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>COMUNAL SANTA TERESA</t>
+        </is>
       </c>
       <c r="P179" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R179" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13727,10 +15517,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O180" t="n">
-        <v>2026</v>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
       </c>
       <c r="P180" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R180" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13801,10 +15601,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O181" t="n">
-        <v>2026</v>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>1201 PAUL HARRIS/1201 PAUL HARRIS</t>
+        </is>
       </c>
       <c r="P181" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R181" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13875,10 +15685,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O182" t="n">
-        <v>2026</v>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA/1110 REPUBLICA DE PANAMA</t>
+        </is>
       </c>
       <c r="P182" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R182" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -13949,10 +15769,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O183" t="n">
-        <v>2026</v>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>0045 SAN ANTONIO/0045 SAN ANTONIO</t>
+        </is>
       </c>
       <c r="P183" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R183" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14023,10 +15853,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O184" t="n">
-        <v>2026</v>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>343 SAN PEDRO DE CHOQUE</t>
+        </is>
       </c>
       <c r="P184" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R184" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14097,10 +15937,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O185" t="n">
-        <v>2026</v>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>CORONEL JOSE GALVEZ</t>
+        </is>
       </c>
       <c r="P185" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R185" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14171,10 +16021,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O186" t="n">
-        <v>2026</v>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>2023 AUGUSTO SALAZAR BONDY/2023 AUGUSTO SALAZAR BONDY/2023 AUGUSTO SALAZAR BONDY/2023 AUGUSTO SALAZAR BONDY</t>
+        </is>
       </c>
       <c r="P186" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R186" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14245,10 +16105,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O187" t="n">
-        <v>2026</v>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>047 SEÑOR DE LOS MILAGROS/047 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P187" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R187" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14319,10 +16189,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O188" t="n">
-        <v>2026</v>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>LIBERTAD/LIBERTAD/LIBERTAD</t>
+        </is>
       </c>
       <c r="P188" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R188" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14393,10 +16273,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O189" t="n">
-        <v>2026</v>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>7055 TUPAC AMARU II/7055 TUPAC AMARU II/7055 TUPAC AMARU II</t>
+        </is>
       </c>
       <c r="P189" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R189" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14467,10 +16357,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O190" t="n">
-        <v>2026</v>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>019 MARIA MONTESSORI</t>
+        </is>
       </c>
       <c r="P190" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R190" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14541,10 +16441,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O191" t="n">
-        <v>2026</v>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS/3066 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P191" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R191" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14615,10 +16525,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O192" t="n">
-        <v>2026</v>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>FELIPE SANTIAGO ESTENOS/FELIPE SANTIAGO ESTENOS/FELIPE SANTIAGO ESTENOS</t>
+        </is>
       </c>
       <c r="P192" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R192" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14689,10 +16609,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O193" t="n">
-        <v>2026</v>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>2085 SAN AGUSTIN/2085 SAN AGUSTIN</t>
+        </is>
       </c>
       <c r="P193" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R193" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14763,10 +16693,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O194" t="n">
-        <v>2026</v>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>1169 ALMIRANTE MIGUEL GRAU S/1169 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+        </is>
       </c>
       <c r="P194" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R194" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14837,10 +16777,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O195" t="n">
-        <v>2026</v>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>3012 JESUS DIVINO MAESTRO</t>
+        </is>
       </c>
       <c r="P195" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R195" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14911,10 +16861,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O196" t="n">
-        <v>2026</v>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>0076 MARIA AUXILIADORA/0076 MARIA AUXILIADORA</t>
+        </is>
       </c>
       <c r="P196" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R196" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -14985,10 +16945,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O197" t="n">
-        <v>2026</v>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>2071 CESAR VALLEJO/2071 CESAR VALLEJO/2071 CESAR VALLEJO/2071 CESAR VALLEJO</t>
+        </is>
       </c>
       <c r="P197" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R197" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15059,10 +17029,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O198" t="n">
-        <v>2026</v>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>2035 FERNANDO BELAUNDE TERRY</t>
+        </is>
       </c>
       <c r="P198" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R198" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15133,10 +17113,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O199" t="n">
-        <v>2026</v>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>109 SAN JOSE</t>
+        </is>
       </c>
       <c r="P199" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R199" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15207,10 +17197,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O200" t="n">
-        <v>2026</v>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>526 SANTISIMA VIRGEN DEL PERPETUO SOCORRO</t>
+        </is>
       </c>
       <c r="P200" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R200" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15281,10 +17281,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O201" t="n">
-        <v>2026</v>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>0024 PEDRO ENRIQUE GONZALES SOTO</t>
+        </is>
       </c>
       <c r="P201" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R201" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15355,10 +17365,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O202" t="n">
-        <v>2026</v>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
       </c>
       <c r="P202" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R202" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15429,10 +17449,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O203" t="n">
-        <v>2026</v>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>161 MOISES COLONIA TRINIDAD/161 MOISES COLONIA TRINIDAD/161 MOISES COLONIA TRINIDAD</t>
+        </is>
       </c>
       <c r="P203" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R203" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15503,10 +17533,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O204" t="n">
-        <v>2026</v>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>536 AMIGUITOS DE JESUS</t>
+        </is>
       </c>
       <c r="P204" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R204" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15577,10 +17617,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O205" t="n">
-        <v>2026</v>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>341 EL RETABLO</t>
+        </is>
       </c>
       <c r="P205" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R205" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15651,10 +17701,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O206" t="n">
-        <v>2026</v>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>0038 SAN MARTIN DE PORRES/0038 SAN MARTIN DE PORRES</t>
+        </is>
       </c>
       <c r="P206" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R206" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15725,10 +17785,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O207" t="n">
-        <v>2026</v>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>564 LOS JILGUEROS DE VILLA VENTURO</t>
+        </is>
       </c>
       <c r="P207" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R207" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15799,10 +17869,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O208" t="n">
-        <v>2026</v>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>0011 MADRE LORETO GABARRE</t>
+        </is>
       </c>
       <c r="P208" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R208" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15873,10 +17953,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O209" t="n">
-        <v>2026</v>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>6059 SAGRADO CORAZON DE JESUS/6059 SAGRADO CORAZON DE JESUS/6059 SAGRADO CORAZON DE JESUS</t>
+        </is>
       </c>
       <c r="P209" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R209" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -15947,10 +18037,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O210" t="n">
-        <v>2026</v>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>075 SANTA MARIA DE GUADALUPE</t>
+        </is>
       </c>
       <c r="P210" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R210" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16021,10 +18121,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O211" t="n">
-        <v>2026</v>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>MICAELA BASTIDAS</t>
+        </is>
       </c>
       <c r="P211" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R211" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16095,10 +18205,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O212" t="n">
-        <v>2026</v>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>1040 REPUBLICA DE HAITI/1040 REPUBLICA DE HAITI</t>
+        </is>
       </c>
       <c r="P212" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R212" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16169,10 +18289,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O213" t="n">
-        <v>2026</v>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>0014 ANDRES BELLO</t>
+        </is>
       </c>
       <c r="P213" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R213" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16243,10 +18373,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O214" t="n">
-        <v>2026</v>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>0038 SAN MARTIN DE PORRES/0038 SAN MARTIN DE PORRES</t>
+        </is>
       </c>
       <c r="P214" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R214" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16317,10 +18457,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O215" t="n">
-        <v>2026</v>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>587 LOS ANGELES DE LA GUARDA</t>
+        </is>
       </c>
       <c r="P215" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R215" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16391,10 +18541,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O216" t="n">
-        <v>2026</v>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>0045 SAN ANTONIO/0045 SAN ANTONIO</t>
+        </is>
       </c>
       <c r="P216" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R216" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16465,10 +18625,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O217" t="n">
-        <v>2026</v>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>0093 FERNANDO BELAUNDE TERRY</t>
+        </is>
       </c>
       <c r="P217" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R217" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16539,10 +18709,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O218" t="n">
-        <v>2026</v>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>0099 OSCAR MIRO QUESADA DE LA GUERRA/0099 OSCAR MIRO QUESADA DE LA GUERRA</t>
+        </is>
       </c>
       <c r="P218" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R218" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16611,10 +18791,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O219" t="n">
-        <v>2026</v>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI/1088 FRANCISCO BOLOGNESI</t>
+        </is>
       </c>
       <c r="P219" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R219" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16683,10 +18873,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O220" t="n">
-        <v>2026</v>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>8157 REPUBLICA DE FRANCIA</t>
+        </is>
       </c>
       <c r="P220" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R220" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16755,10 +18955,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O221" t="n">
-        <v>2026</v>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>7062 NACIONES UNIDAS/7062 NACIONES UNIDAS</t>
+        </is>
       </c>
       <c r="P221" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R221" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16827,10 +19037,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O222" t="n">
-        <v>2026</v>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>MANUEL SCORZA/MANUEL SCORZA</t>
+        </is>
       </c>
       <c r="P222" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R222" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16899,10 +19119,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O223" t="n">
-        <v>2026</v>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>7041 VIRGEN DE LA MERCED/7041 VIRGEN DE LA MERCED</t>
+        </is>
       </c>
       <c r="P223" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R223" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -16971,10 +19201,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O224" t="n">
-        <v>2026</v>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>7041 VIRGEN DE LA MERCED/7041 VIRGEN DE LA MERCED</t>
+        </is>
       </c>
       <c r="P224" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R224" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17043,10 +19283,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O225" t="n">
-        <v>2026</v>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>0101 RAYITO DE LUZ</t>
+        </is>
       </c>
       <c r="P225" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R225" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17115,10 +19365,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O226" t="n">
-        <v>2026</v>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>JOSE DE LA RIVA AGUERO Y OSMA</t>
+        </is>
       </c>
       <c r="P226" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R226" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17187,10 +19447,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O227" t="n">
-        <v>2026</v>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>JOSE SANTOS CHOCANO</t>
+        </is>
       </c>
       <c r="P227" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R227" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17259,10 +19529,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O228" t="n">
-        <v>2026</v>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>SEMILLITAS II</t>
+        </is>
       </c>
       <c r="P228" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R228" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17331,10 +19611,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O229" t="n">
-        <v>2026</v>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>1107 JAVIER PRADO/1107 JAVIER PRADO/1107 JAVIER PRADO</t>
+        </is>
       </c>
       <c r="P229" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R229" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17403,10 +19693,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O230" t="n">
-        <v>2026</v>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION/25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION/25 NUESTRA SEÑORA DE LA INMACULADA CONCEPCION</t>
+        </is>
       </c>
       <c r="P230" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R230" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17475,10 +19775,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O231" t="n">
-        <v>2026</v>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>8179 RAMIRO PRIALE</t>
+        </is>
       </c>
       <c r="P231" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R231" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17547,10 +19857,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O232" t="n">
-        <v>2026</v>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
+        </is>
       </c>
       <c r="P232" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R232" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17619,10 +19939,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O233" t="n">
-        <v>2026</v>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>0140 SANTIAGO ANTUNEZ DE MAYOLO/0140 SANTIAGO ANTUNEZ DE MAYOLO</t>
+        </is>
       </c>
       <c r="P233" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R233" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17691,10 +20021,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O234" t="n">
-        <v>2026</v>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>8174</t>
+        </is>
       </c>
       <c r="P234" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R234" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17763,10 +20103,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O235" t="n">
-        <v>2026</v>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>1285/1285</t>
+        </is>
       </c>
       <c r="P235" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R235" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17835,10 +20185,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O236" t="n">
-        <v>2026</v>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>0004 MARIANO MELGAR/0004 MARIANO MELGAR</t>
+        </is>
       </c>
       <c r="P236" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R236" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17907,10 +20267,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O237" t="n">
-        <v>2026</v>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>103 NIÑO JESUS DE PRAGA</t>
+        </is>
       </c>
       <c r="P237" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R237" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -17979,10 +20349,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O238" t="n">
-        <v>2026</v>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>104 VIRGEN DE LA PUERTA</t>
+        </is>
       </c>
       <c r="P238" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R238" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18051,10 +20431,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O239" t="n">
-        <v>2026</v>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>16 VIRGEN DE LOURDES</t>
+        </is>
       </c>
       <c r="P239" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R239" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18123,10 +20513,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O240" t="n">
-        <v>2026</v>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>WARMA KUYAY</t>
+        </is>
       </c>
       <c r="P240" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R240" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18195,10 +20595,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O241" t="n">
-        <v>2026</v>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>04 NIÑO JESUS DE PRAGA</t>
+        </is>
       </c>
       <c r="P241" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R241" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18267,10 +20677,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O242" t="n">
-        <v>2026</v>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>6081 MANUEL SCORZA TORRES/6081 MANUEL SCORZA TORRES/6081 MANUEL SCORZA TORRES/6081 MANUEL SCORZA TORRES</t>
+        </is>
       </c>
       <c r="P242" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R242" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18339,10 +20759,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O243" t="n">
-        <v>2026</v>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>1169 ALMIRANTE MIGUEL GRAU S/1169 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+        </is>
       </c>
       <c r="P243" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R243" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18411,10 +20841,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O244" t="n">
-        <v>2026</v>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>50 LA SAGRADA FAMILIA/CORCOVADO</t>
+        </is>
       </c>
       <c r="P244" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R244" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18483,10 +20923,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O245" t="n">
-        <v>2026</v>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
       </c>
       <c r="P245" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R245" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18555,10 +21005,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O246" t="n">
-        <v>2026</v>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>098 NIÑOS DE SAN JUDAS TADEO</t>
+        </is>
       </c>
       <c r="P246" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R246" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18627,10 +21087,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O247" t="n">
-        <v>2026</v>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>095 MEDALLA MILAGROSA</t>
+        </is>
       </c>
       <c r="P247" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R247" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18699,10 +21169,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O248" t="n">
-        <v>2026</v>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>53 MI NIÑITO JESUS</t>
+        </is>
       </c>
       <c r="P248" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R248" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18771,10 +21251,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O249" t="n">
-        <v>2026</v>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>79 VIRGEN DEL CARMEN</t>
+        </is>
       </c>
       <c r="P249" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R249" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18843,10 +21333,20 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
-      <c r="O250" t="n">
-        <v>2026</v>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>522 MARIA INMACULADA</t>
+        </is>
       </c>
       <c r="P250" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R250" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18915,10 +21415,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O251" t="n">
-        <v>2026</v>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>115-11 SAGRADO CORAZON DE JESUS</t>
+        </is>
       </c>
       <c r="P251" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R251" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -18987,10 +21497,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O252" t="n">
-        <v>2026</v>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>110 SAN MARCOS/110 SAN MARCOS</t>
+        </is>
       </c>
       <c r="P252" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R252" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19059,10 +21579,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O253" t="n">
-        <v>2026</v>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>1188 JUAN PABLO II/1188 JUAN PABLO II</t>
+        </is>
       </c>
       <c r="P253" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R253" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19131,10 +21661,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O254" t="n">
-        <v>2026</v>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>7102 SAN FRANCISCO DE ASIS/7102 SAN FRANCISCO DE ASIS/7102 SAN FRANCISCO DE ASIS</t>
+        </is>
       </c>
       <c r="P254" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R254" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19203,10 +21743,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O255" t="n">
-        <v>2026</v>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>LUIS ENRIQUE XVII</t>
+        </is>
       </c>
       <c r="P255" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R255" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19275,10 +21825,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O256" t="n">
-        <v>2026</v>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>LUIS ENRIQUE XIV</t>
+        </is>
       </c>
       <c r="P256" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R256" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19347,10 +21907,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O257" t="n">
-        <v>2026</v>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>6069 PACHACUTEC/6069 PACHACUTEC/6069 PACHACUTEC/6069 PACHACUTEC</t>
+        </is>
       </c>
       <c r="P257" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R257" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19419,10 +21989,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O258" t="n">
-        <v>2026</v>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>1037 RAMON ESPINOZA/106 RAMON ESPINOZA/1037 RAMON ESPINOZA</t>
+        </is>
       </c>
       <c r="P258" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R258" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19491,10 +22071,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O259" t="n">
-        <v>2026</v>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>0013 BERNARDO O'HIGGINS/0013 BERNARDO O'HIGGINS</t>
+        </is>
       </c>
       <c r="P259" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R259" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19563,10 +22153,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O260" t="n">
-        <v>2026</v>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>2053 FRANCISCO BOLOGNESI CERVANTES/2053 FRANCISCO BOLOGNESI CERVANTES/2053 FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
       </c>
       <c r="P260" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R260" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19635,10 +22235,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O261" t="n">
-        <v>2026</v>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>27 DE MARZO/27 DE MARZO</t>
+        </is>
       </c>
       <c r="P261" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R261" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19707,10 +22317,20 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
-      <c r="O262" t="n">
-        <v>2026</v>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>550 REPUBLICA DEL JAPON</t>
+        </is>
       </c>
       <c r="P262" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R262" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19779,10 +22399,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O263" t="n">
-        <v>2026</v>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>0073 BENITO JUAREZ/0073 BENITO JUAREZ</t>
+        </is>
       </c>
       <c r="P263" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R263" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19851,10 +22481,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O264" t="n">
-        <v>2026</v>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>1005 JORGE CHAVEZ DARTNELL</t>
+        </is>
       </c>
       <c r="P264" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R264" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19923,10 +22563,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O265" t="n">
-        <v>2026</v>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>3017 INMACULADA CONCEPCION/3017 INMACULADA CONCEPCION</t>
+        </is>
       </c>
       <c r="P265" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R265" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -19995,10 +22645,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O266" t="n">
-        <v>2026</v>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>3030/3030/3030 SANTISIMA CRUZ</t>
+        </is>
       </c>
       <c r="P266" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R266" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20039,10 +22699,12 @@
       <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
-      <c r="O267" t="n">
-        <v>2026</v>
-      </c>
-      <c r="P267" t="inlineStr">
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R267" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20111,10 +22773,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O268" t="n">
-        <v>2026</v>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>1073 HERMANN BUSE DE LA GUERRA/1073 HERMANN BUSE DE LA GUERRA</t>
+        </is>
       </c>
       <c r="P268" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R268" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20183,10 +22855,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O269" t="n">
-        <v>2026</v>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>1107 JAVIER PRADO/1107 JAVIER PRADO/1107 JAVIER PRADO</t>
+        </is>
       </c>
       <c r="P269" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R269" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20255,10 +22937,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O270" t="n">
-        <v>2026</v>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>PASITOS DEL SABER</t>
+        </is>
       </c>
       <c r="P270" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R270" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20327,10 +23019,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O271" t="n">
-        <v>2026</v>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>1244 MICAELA BASTIDAS/1244 MICAELA BASTIDAS/1244 MICAELA BASTIDAS</t>
+        </is>
       </c>
       <c r="P271" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R271" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20399,10 +23101,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O272" t="n">
-        <v>2026</v>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>0072 SANTA ROSITA DE LIMA</t>
+        </is>
       </c>
       <c r="P272" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R272" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20471,10 +23183,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O273" t="n">
-        <v>2026</v>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>56 NUESTRA SEÑORA MARIA AUXILIADORA</t>
+        </is>
       </c>
       <c r="P273" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R273" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20543,10 +23265,20 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
-      <c r="O274" t="n">
-        <v>2026</v>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>1188 JUAN PABLO II/1188 JUAN PABLO II</t>
+        </is>
       </c>
       <c r="P274" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R274" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20615,10 +23347,20 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
-      <c r="O275" t="n">
-        <v>2026</v>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>1214 SEÑOR DE LOS MILAGROS</t>
+        </is>
       </c>
       <c r="P275" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R275" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20687,10 +23429,20 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
-      <c r="O276" t="n">
-        <v>2026</v>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>345 RAYITO DE SOL</t>
+        </is>
       </c>
       <c r="P276" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R276" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20759,10 +23511,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O277" t="n">
-        <v>2026</v>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>356 ANGELITOS DEL ALAMO</t>
+        </is>
       </c>
       <c r="P277" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R277" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20831,10 +23593,20 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
-      <c r="O278" t="n">
-        <v>2026</v>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>LOS NARANJOS</t>
+        </is>
       </c>
       <c r="P278" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R278" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>
@@ -20903,10 +23675,20 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
-      <c r="O279" t="n">
-        <v>2026</v>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>1187 SAN CAYETANO/1187 SAN CAYETANO</t>
+        </is>
       </c>
       <c r="P279" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>2026</v>
+      </c>
+      <c r="R279" t="inlineStr">
         <is>
           <t>DRELM</t>
         </is>

--- a/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
+++ b/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
@@ -7689,7 +7689,11 @@
           <t>VILLA EL SALVADOR</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>VILLA EL SALVADOR</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>150142</t>

--- a/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
+++ b/output/bases_limpias/Grupo_01_MOBILIARIO_Y_EQUIPO/df_drelm_mobiliario.xlsx
@@ -419,17 +419,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>CODIGO MODULAR</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>NOMBRE DE INSTITUCION EDUCATIVA</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>CODIGO DE LOCAL</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,17 +439,17 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>mobiliario}</t>
+          <t>mobiliario</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>nan (1)</t>
+          <t>nan_1</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>nan (2)</t>
+          <t>nan_2</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -489,7 +489,7 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
